--- a/Assets/@Resources/Data/Excel/EquipEnhanceData.xlsx
+++ b/Assets/@Resources/Data/Excel/EquipEnhanceData.xlsx
@@ -556,10 +556,10 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>11001</v>
@@ -582,10 +582,10 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>11002</v>
@@ -608,10 +608,10 @@
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>11003</v>
@@ -634,10 +634,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>11004</v>
@@ -660,10 +660,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>11005</v>
@@ -686,10 +686,10 @@
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
         <v>11006</v>
@@ -712,10 +712,10 @@
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G10" t="n">
         <v>11007</v>
@@ -738,10 +738,10 @@
         <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
         <v>11008</v>
@@ -764,10 +764,10 @@
         <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>11009</v>
@@ -790,10 +790,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>11003</v>
@@ -816,10 +816,10 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>11004</v>
@@ -842,10 +842,10 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>11005</v>
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>11006</v>
@@ -894,10 +894,10 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>11007</v>
@@ -920,10 +920,10 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>11008</v>
@@ -946,10 +946,10 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>11009</v>
@@ -972,10 +972,10 @@
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>11010</v>
@@ -998,10 +998,10 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>11001</v>
@@ -1024,10 +1024,10 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>11005</v>
@@ -1050,10 +1050,10 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>11006</v>
@@ -1076,10 +1076,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>11007</v>
@@ -1102,10 +1102,10 @@
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>11008</v>
@@ -1128,10 +1128,10 @@
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>11009</v>
@@ -1154,10 +1154,10 @@
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>11010</v>
@@ -1180,10 +1180,10 @@
         <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>11001</v>
@@ -1206,10 +1206,10 @@
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>11002</v>
@@ -1232,10 +1232,10 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>11003</v>
@@ -1258,10 +1258,10 @@
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>11007</v>
@@ -1284,10 +1284,10 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>11008</v>
@@ -1310,10 +1310,10 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>11009</v>
@@ -1336,10 +1336,10 @@
         <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>11010</v>
@@ -1362,10 +1362,10 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>11001</v>
@@ -1388,10 +1388,10 @@
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>11002</v>
@@ -1414,10 +1414,10 @@
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1</v>
+        <v>7</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>11003</v>
@@ -1440,10 +1440,10 @@
         <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>11004</v>
@@ -1466,10 +1466,10 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>11005</v>
@@ -1492,10 +1492,10 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>11009</v>
@@ -1518,10 +1518,10 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
         <v>11010</v>
@@ -1544,10 +1544,10 @@
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>11001</v>
@@ -1570,10 +1570,10 @@
         <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
         <v>11002</v>
@@ -1596,10 +1596,10 @@
         <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
         <v>11003</v>
@@ -1622,10 +1622,10 @@
         <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
         <v>11004</v>
@@ -1648,10 +1648,10 @@
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
         <v>11005</v>
@@ -1674,10 +1674,10 @@
         <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
         <v>11006</v>
@@ -1700,10 +1700,10 @@
         <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>11007</v>
@@ -1726,10 +1726,10 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>11001</v>
@@ -1752,10 +1752,10 @@
         <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>0.15</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
         <v>11002</v>
@@ -1778,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
         <v>11003</v>
@@ -1804,10 +1804,10 @@
         <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>0.15</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
         <v>11004</v>
@@ -1830,10 +1830,10 @@
         <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>0.15</v>
+        <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
         <v>11005</v>
@@ -1856,10 +1856,10 @@
         <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>0.15</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>11006</v>
@@ -1882,10 +1882,10 @@
         <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>0.15</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
         <v>11007</v>
@@ -1908,10 +1908,10 @@
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G56" t="n">
         <v>11008</v>
@@ -1934,10 +1934,10 @@
         <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>0.15</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>11009</v>
@@ -1960,10 +1960,10 @@
         <v>14</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G58" t="n">
         <v>11001</v>
@@ -1986,10 +1986,10 @@
         <v>18</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G59" t="n">
         <v>11002</v>
@@ -2012,10 +2012,10 @@
         <v>21</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G60" t="n">
         <v>11003</v>
@@ -2038,10 +2038,10 @@
         <v>24</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G61" t="n">
         <v>11004</v>
@@ -2064,10 +2064,10 @@
         <v>28</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G62" t="n">
         <v>11005</v>
@@ -2090,10 +2090,10 @@
         <v>32</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G63" t="n">
         <v>11006</v>
@@ -2116,10 +2116,10 @@
         <v>35</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G64" t="n">
         <v>11007</v>
@@ -2142,10 +2142,10 @@
         <v>38</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G65" t="n">
         <v>11008</v>
@@ -2168,10 +2168,10 @@
         <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G66" t="n">
         <v>11009</v>
@@ -2194,10 +2194,10 @@
         <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
         <v>11003</v>
@@ -2220,10 +2220,10 @@
         <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
         <v>11004</v>
@@ -2246,10 +2246,10 @@
         <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>11005</v>
@@ -2272,10 +2272,10 @@
         <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
         <v>11006</v>
@@ -2298,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G71" t="n">
         <v>11007</v>
@@ -2324,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
         <v>11008</v>
@@ -2350,10 +2350,10 @@
         <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
         <v>11009</v>
@@ -2376,10 +2376,10 @@
         <v>11</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G74" t="n">
         <v>11010</v>
@@ -2402,10 +2402,10 @@
         <v>12</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G75" t="n">
         <v>11001</v>
@@ -2428,10 +2428,10 @@
         <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
         <v>11005</v>
@@ -2454,10 +2454,10 @@
         <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G77" t="n">
         <v>11006</v>
@@ -2480,10 +2480,10 @@
         <v>9</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G78" t="n">
         <v>11007</v>
@@ -2506,10 +2506,10 @@
         <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
         <v>11008</v>
@@ -2532,10 +2532,10 @@
         <v>12</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
         <v>11009</v>
@@ -2558,10 +2558,10 @@
         <v>14</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G81" t="n">
         <v>11010</v>
@@ -2584,10 +2584,10 @@
         <v>15</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G82" t="n">
         <v>11001</v>
@@ -2610,10 +2610,10 @@
         <v>16</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G83" t="n">
         <v>11002</v>
@@ -2636,10 +2636,10 @@
         <v>18</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G84" t="n">
         <v>11003</v>
@@ -2662,10 +2662,10 @@
         <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G85" t="n">
         <v>11007</v>
@@ -2688,10 +2688,10 @@
         <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G86" t="n">
         <v>11008</v>
@@ -2714,10 +2714,10 @@
         <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G87" t="n">
         <v>11009</v>
@@ -2740,10 +2740,10 @@
         <v>9</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G88" t="n">
         <v>11010</v>
@@ -2766,10 +2766,10 @@
         <v>10</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G89" t="n">
         <v>11001</v>
@@ -2792,10 +2792,10 @@
         <v>11</v>
       </c>
       <c r="E90" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
         <v>11002</v>
@@ -2818,10 +2818,10 @@
         <v>12</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G91" t="n">
         <v>11003</v>
@@ -2844,10 +2844,10 @@
         <v>14</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G92" t="n">
         <v>11004</v>
@@ -2870,10 +2870,10 @@
         <v>15</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G93" t="n">
         <v>11005</v>
@@ -2896,10 +2896,10 @@
         <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G94" t="n">
         <v>11009</v>
@@ -2922,10 +2922,10 @@
         <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
         <v>11010</v>
@@ -2948,10 +2948,10 @@
         <v>8</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G96" t="n">
         <v>11001</v>
@@ -2974,10 +2974,10 @@
         <v>9</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G97" t="n">
         <v>11002</v>
@@ -3000,10 +3000,10 @@
         <v>10</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G98" t="n">
         <v>11003</v>
@@ -3026,10 +3026,10 @@
         <v>11</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G99" t="n">
         <v>11004</v>
@@ -3052,10 +3052,10 @@
         <v>12</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G100" t="n">
         <v>11005</v>
@@ -3078,10 +3078,10 @@
         <v>14</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G101" t="n">
         <v>11006</v>
@@ -3104,10 +3104,10 @@
         <v>15</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G102" t="n">
         <v>11007</v>
@@ -3130,10 +3130,10 @@
         <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G103" t="n">
         <v>11001</v>
@@ -3156,10 +3156,10 @@
         <v>8</v>
       </c>
       <c r="E104" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>11002</v>
@@ -3182,10 +3182,10 @@
         <v>9</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
         <v>11003</v>
@@ -3208,10 +3208,10 @@
         <v>10</v>
       </c>
       <c r="E106" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G106" t="n">
         <v>11004</v>
@@ -3234,10 +3234,10 @@
         <v>12</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G107" t="n">
         <v>11005</v>
@@ -3260,10 +3260,10 @@
         <v>14</v>
       </c>
       <c r="E108" t="n">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G108" t="n">
         <v>11006</v>
@@ -3286,10 +3286,10 @@
         <v>15</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3</v>
+        <v>7</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G109" t="n">
         <v>11007</v>
@@ -3312,10 +3312,10 @@
         <v>16</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G110" t="n">
         <v>11008</v>
@@ -3338,10 +3338,10 @@
         <v>18</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G111" t="n">
         <v>11009</v>
@@ -3364,10 +3364,10 @@
         <v>24</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G112" t="n">
         <v>11001</v>
@@ -3390,10 +3390,10 @@
         <v>30</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G113" t="n">
         <v>11002</v>
@@ -3416,10 +3416,10 @@
         <v>36</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G114" t="n">
         <v>11003</v>
@@ -3442,10 +3442,10 @@
         <v>42</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G115" t="n">
         <v>11004</v>
@@ -3468,10 +3468,10 @@
         <v>48</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G116" t="n">
         <v>11005</v>
@@ -3494,10 +3494,10 @@
         <v>54</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G117" t="n">
         <v>11006</v>
@@ -3520,10 +3520,10 @@
         <v>60</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G118" t="n">
         <v>11007</v>
@@ -3546,10 +3546,10 @@
         <v>66</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G119" t="n">
         <v>11008</v>
@@ -3572,10 +3572,10 @@
         <v>72</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G120" t="n">
         <v>11009</v>
@@ -3598,10 +3598,10 @@
         <v>6</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
         <v>11003</v>
@@ -3624,10 +3624,10 @@
         <v>8</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G122" t="n">
         <v>11004</v>
@@ -3650,10 +3650,10 @@
         <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G123" t="n">
         <v>11005</v>
@@ -3676,10 +3676,10 @@
         <v>10</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G124" t="n">
         <v>11006</v>
@@ -3702,10 +3702,10 @@
         <v>12</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G125" t="n">
         <v>11007</v>
@@ -3728,10 +3728,10 @@
         <v>14</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G126" t="n">
         <v>11008</v>
@@ -3754,10 +3754,10 @@
         <v>15</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G127" t="n">
         <v>11009</v>
@@ -3780,10 +3780,10 @@
         <v>16</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G128" t="n">
         <v>11010</v>
@@ -3806,10 +3806,10 @@
         <v>18</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G129" t="n">
         <v>11001</v>
@@ -3832,10 +3832,10 @@
         <v>10</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G130" t="n">
         <v>11005</v>
@@ -3858,10 +3858,10 @@
         <v>12</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G131" t="n">
         <v>11006</v>
@@ -3884,10 +3884,10 @@
         <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G132" t="n">
         <v>11007</v>
@@ -3910,10 +3910,10 @@
         <v>18</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G133" t="n">
         <v>11008</v>
@@ -3936,10 +3936,10 @@
         <v>20</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G134" t="n">
         <v>11009</v>
@@ -3962,10 +3962,10 @@
         <v>22</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G135" t="n">
         <v>11010</v>
@@ -3988,10 +3988,10 @@
         <v>25</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G136" t="n">
         <v>11001</v>
@@ -4014,10 +4014,10 @@
         <v>28</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G137" t="n">
         <v>11002</v>
@@ -4040,10 +4040,10 @@
         <v>30</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G138" t="n">
         <v>11003</v>
@@ -4066,10 +4066,10 @@
         <v>8</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G139" t="n">
         <v>11007</v>
@@ -4092,10 +4092,10 @@
         <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G140" t="n">
         <v>11008</v>
@@ -4118,10 +4118,10 @@
         <v>12</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G141" t="n">
         <v>11009</v>
@@ -4144,10 +4144,10 @@
         <v>14</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G142" t="n">
         <v>11010</v>
@@ -4170,10 +4170,10 @@
         <v>16</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G143" t="n">
         <v>11001</v>
@@ -4196,10 +4196,10 @@
         <v>18</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G144" t="n">
         <v>11002</v>
@@ -4222,10 +4222,10 @@
         <v>20</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3</v>
+        <v>7</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G145" t="n">
         <v>11003</v>
@@ -4248,10 +4248,10 @@
         <v>22</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G146" t="n">
         <v>11004</v>
@@ -4274,10 +4274,10 @@
         <v>24</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G147" t="n">
         <v>11005</v>
@@ -4300,10 +4300,10 @@
         <v>8</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G148" t="n">
         <v>11009</v>
@@ -4326,10 +4326,10 @@
         <v>10</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G149" t="n">
         <v>11010</v>
@@ -4352,10 +4352,10 @@
         <v>12</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G150" t="n">
         <v>11001</v>
@@ -4378,10 +4378,10 @@
         <v>14</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G151" t="n">
         <v>11002</v>
@@ -4404,10 +4404,10 @@
         <v>16</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G152" t="n">
         <v>11003</v>
@@ -4430,10 +4430,10 @@
         <v>18</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G153" t="n">
         <v>11004</v>
@@ -4456,10 +4456,10 @@
         <v>20</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G154" t="n">
         <v>11005</v>
@@ -4482,10 +4482,10 @@
         <v>22</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G155" t="n">
         <v>11006</v>
@@ -4508,10 +4508,10 @@
         <v>24</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G156" t="n">
         <v>11007</v>
@@ -4534,10 +4534,10 @@
         <v>10</v>
       </c>
       <c r="E157" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G157" t="n">
         <v>11001</v>
@@ -4560,10 +4560,10 @@
         <v>12</v>
       </c>
       <c r="E158" t="n">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="F158" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G158" t="n">
         <v>11002</v>
@@ -4586,10 +4586,10 @@
         <v>15</v>
       </c>
       <c r="E159" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="F159" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G159" t="n">
         <v>11003</v>
@@ -4612,10 +4612,10 @@
         <v>18</v>
       </c>
       <c r="E160" t="n">
-        <v>0.45</v>
+        <v>4</v>
       </c>
       <c r="F160" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G160" t="n">
         <v>11004</v>
@@ -4638,10 +4638,10 @@
         <v>20</v>
       </c>
       <c r="E161" t="n">
-        <v>0.45</v>
+        <v>5</v>
       </c>
       <c r="F161" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G161" t="n">
         <v>11005</v>
@@ -4664,10 +4664,10 @@
         <v>22</v>
       </c>
       <c r="E162" t="n">
-        <v>0.45</v>
+        <v>6</v>
       </c>
       <c r="F162" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G162" t="n">
         <v>11006</v>
@@ -4690,10 +4690,10 @@
         <v>25</v>
       </c>
       <c r="E163" t="n">
-        <v>0.45</v>
+        <v>7</v>
       </c>
       <c r="F163" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G163" t="n">
         <v>11007</v>
@@ -4716,10 +4716,10 @@
         <v>28</v>
       </c>
       <c r="E164" t="n">
-        <v>0.45</v>
+        <v>8</v>
       </c>
       <c r="F164" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G164" t="n">
         <v>11008</v>
@@ -4742,10 +4742,10 @@
         <v>30</v>
       </c>
       <c r="E165" t="n">
-        <v>0.45</v>
+        <v>9</v>
       </c>
       <c r="F165" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G165" t="n">
         <v>11009</v>
@@ -4768,10 +4768,10 @@
         <v>36</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G166" t="n">
         <v>11001</v>
@@ -4794,10 +4794,10 @@
         <v>45</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G167" t="n">
         <v>11002</v>
@@ -4820,10 +4820,10 @@
         <v>54</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G168" t="n">
         <v>11003</v>
@@ -4846,10 +4846,10 @@
         <v>63</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G169" t="n">
         <v>11004</v>
@@ -4872,10 +4872,10 @@
         <v>72</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G170" t="n">
         <v>11005</v>
@@ -4898,10 +4898,10 @@
         <v>81</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G171" t="n">
         <v>11006</v>
@@ -4924,10 +4924,10 @@
         <v>90</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G172" t="n">
         <v>11007</v>
@@ -4950,10 +4950,10 @@
         <v>99</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G173" t="n">
         <v>11008</v>
@@ -4976,10 +4976,10 @@
         <v>108</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G174" t="n">
         <v>11009</v>
@@ -5002,10 +5002,10 @@
         <v>10</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G175" t="n">
         <v>11003</v>
@@ -5028,10 +5028,10 @@
         <v>12</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G176" t="n">
         <v>11004</v>
@@ -5054,10 +5054,10 @@
         <v>15</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G177" t="n">
         <v>11005</v>
@@ -5080,10 +5080,10 @@
         <v>18</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G178" t="n">
         <v>11006</v>
@@ -5106,10 +5106,10 @@
         <v>20</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G179" t="n">
         <v>11007</v>
@@ -5132,10 +5132,10 @@
         <v>22</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G180" t="n">
         <v>11008</v>
@@ -5158,10 +5158,10 @@
         <v>25</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G181" t="n">
         <v>11009</v>
@@ -5184,10 +5184,10 @@
         <v>28</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G182" t="n">
         <v>11010</v>
@@ -5210,10 +5210,10 @@
         <v>30</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G183" t="n">
         <v>11001</v>
@@ -5236,10 +5236,10 @@
         <v>16</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G184" t="n">
         <v>11005</v>
@@ -5262,10 +5262,10 @@
         <v>20</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G185" t="n">
         <v>11006</v>
@@ -5288,10 +5288,10 @@
         <v>24</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G186" t="n">
         <v>11007</v>
@@ -5314,10 +5314,10 @@
         <v>28</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G187" t="n">
         <v>11008</v>
@@ -5340,10 +5340,10 @@
         <v>32</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G188" t="n">
         <v>11009</v>
@@ -5366,10 +5366,10 @@
         <v>36</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G189" t="n">
         <v>11010</v>
@@ -5392,10 +5392,10 @@
         <v>40</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G190" t="n">
         <v>11001</v>
@@ -5418,10 +5418,10 @@
         <v>44</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G191" t="n">
         <v>11002</v>
@@ -5444,10 +5444,10 @@
         <v>48</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G192" t="n">
         <v>11003</v>
@@ -5470,10 +5470,10 @@
         <v>12</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G193" t="n">
         <v>11007</v>
@@ -5496,10 +5496,10 @@
         <v>15</v>
       </c>
       <c r="E194" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G194" t="n">
         <v>11008</v>
@@ -5522,10 +5522,10 @@
         <v>18</v>
       </c>
       <c r="E195" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G195" t="n">
         <v>11009</v>
@@ -5548,10 +5548,10 @@
         <v>21</v>
       </c>
       <c r="E196" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G196" t="n">
         <v>11010</v>
@@ -5574,10 +5574,10 @@
         <v>24</v>
       </c>
       <c r="E197" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G197" t="n">
         <v>11001</v>
@@ -5600,10 +5600,10 @@
         <v>27</v>
       </c>
       <c r="E198" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G198" t="n">
         <v>11002</v>
@@ -5626,10 +5626,10 @@
         <v>30</v>
       </c>
       <c r="E199" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G199" t="n">
         <v>11003</v>
@@ -5652,10 +5652,10 @@
         <v>33</v>
       </c>
       <c r="E200" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G200" t="n">
         <v>11004</v>
@@ -5678,10 +5678,10 @@
         <v>36</v>
       </c>
       <c r="E201" t="n">
-        <v>0.4</v>
+        <v>9</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G201" t="n">
         <v>11005</v>
@@ -5704,10 +5704,10 @@
         <v>12</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G202" t="n">
         <v>11009</v>
@@ -5730,10 +5730,10 @@
         <v>15</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G203" t="n">
         <v>11010</v>
@@ -5756,10 +5756,10 @@
         <v>18</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G204" t="n">
         <v>11001</v>
@@ -5782,10 +5782,10 @@
         <v>21</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G205" t="n">
         <v>11002</v>
@@ -5808,10 +5808,10 @@
         <v>24</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G206" t="n">
         <v>11003</v>
@@ -5834,10 +5834,10 @@
         <v>27</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G207" t="n">
         <v>11004</v>
@@ -5860,10 +5860,10 @@
         <v>30</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G208" t="n">
         <v>11005</v>
@@ -5886,10 +5886,10 @@
         <v>33</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G209" t="n">
         <v>11006</v>
@@ -5912,10 +5912,10 @@
         <v>36</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G210" t="n">
         <v>11007</v>
@@ -5938,10 +5938,10 @@
         <v>16</v>
       </c>
       <c r="E211" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G211" t="n">
         <v>11001</v>
@@ -5964,10 +5964,10 @@
         <v>20</v>
       </c>
       <c r="E212" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="F212" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G212" t="n">
         <v>11002</v>
@@ -5990,10 +5990,10 @@
         <v>24</v>
       </c>
       <c r="E213" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="F213" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G213" t="n">
         <v>11003</v>
@@ -6016,10 +6016,10 @@
         <v>28</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="F214" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G214" t="n">
         <v>11004</v>
@@ -6042,10 +6042,10 @@
         <v>32</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="F215" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G215" t="n">
         <v>11005</v>
@@ -6068,10 +6068,10 @@
         <v>36</v>
       </c>
       <c r="E216" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="F216" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G216" t="n">
         <v>11006</v>
@@ -6094,10 +6094,10 @@
         <v>40</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="F217" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G217" t="n">
         <v>11007</v>
@@ -6120,10 +6120,10 @@
         <v>44</v>
       </c>
       <c r="E218" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="F218" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G218" t="n">
         <v>11008</v>
@@ -6146,10 +6146,10 @@
         <v>48</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="F219" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G219" t="n">
         <v>11009</v>
@@ -6172,10 +6172,10 @@
         <v>51</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G220" t="n">
         <v>11011</v>
@@ -6198,10 +6198,10 @@
         <v>64</v>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G221" t="n">
         <v>11012</v>
@@ -6224,10 +6224,10 @@
         <v>76</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G222" t="n">
         <v>11013</v>
@@ -6250,10 +6250,10 @@
         <v>89</v>
       </c>
       <c r="E223" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G223" t="n">
         <v>11014</v>
@@ -6276,10 +6276,10 @@
         <v>102</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F224" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G224" t="n">
         <v>11015</v>
@@ -6302,10 +6302,10 @@
         <v>115</v>
       </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F225" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G225" t="n">
         <v>11016</v>
@@ -6328,10 +6328,10 @@
         <v>128</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="G226" t="n">
         <v>11017</v>
@@ -6354,10 +6354,10 @@
         <v>140</v>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G227" t="n">
         <v>11018</v>
@@ -6380,10 +6380,10 @@
         <v>153</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G228" t="n">
         <v>11019</v>
@@ -6406,10 +6406,10 @@
         <v>14</v>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G229" t="n">
         <v>11013</v>
@@ -6432,10 +6432,10 @@
         <v>18</v>
       </c>
       <c r="E230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F230" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G230" t="n">
         <v>11014</v>
@@ -6458,10 +6458,10 @@
         <v>21</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F231" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G231" t="n">
         <v>11015</v>
@@ -6484,10 +6484,10 @@
         <v>24</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F232" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G232" t="n">
         <v>11016</v>
@@ -6510,10 +6510,10 @@
         <v>28</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F233" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G233" t="n">
         <v>11017</v>
@@ -6536,10 +6536,10 @@
         <v>32</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F234" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="G234" t="n">
         <v>11018</v>
@@ -6562,10 +6562,10 @@
         <v>35</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F235" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G235" t="n">
         <v>11019</v>
@@ -6588,10 +6588,10 @@
         <v>38</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F236" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G236" t="n">
         <v>11020</v>
@@ -6614,10 +6614,10 @@
         <v>42</v>
       </c>
       <c r="E237" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F237" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="G237" t="n">
         <v>11011</v>
@@ -6640,10 +6640,10 @@
         <v>22</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G238" t="n">
         <v>11015</v>
@@ -6666,10 +6666,10 @@
         <v>28</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G239" t="n">
         <v>11016</v>
@@ -6692,10 +6692,10 @@
         <v>33</v>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G240" t="n">
         <v>11017</v>
@@ -6718,10 +6718,10 @@
         <v>38</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G241" t="n">
         <v>11018</v>
@@ -6744,10 +6744,10 @@
         <v>44</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G242" t="n">
         <v>11019</v>
@@ -6770,10 +6770,10 @@
         <v>50</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F243" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G243" t="n">
         <v>11020</v>
@@ -6796,10 +6796,10 @@
         <v>55</v>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F244" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G244" t="n">
         <v>11011</v>
@@ -6822,10 +6822,10 @@
         <v>60</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G245" t="n">
         <v>11012</v>
@@ -6848,10 +6848,10 @@
         <v>66</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G246" t="n">
         <v>11013</v>
@@ -6874,10 +6874,10 @@
         <v>18</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G247" t="n">
         <v>11017</v>
@@ -6900,10 +6900,10 @@
         <v>22</v>
       </c>
       <c r="E248" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G248" t="n">
         <v>11018</v>
@@ -6926,10 +6926,10 @@
         <v>27</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G249" t="n">
         <v>11019</v>
@@ -6952,10 +6952,10 @@
         <v>32</v>
       </c>
       <c r="E250" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G250" t="n">
         <v>11020</v>
@@ -6978,10 +6978,10 @@
         <v>36</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F251" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G251" t="n">
         <v>11011</v>
@@ -7004,10 +7004,10 @@
         <v>40</v>
       </c>
       <c r="E252" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G252" t="n">
         <v>11012</v>
@@ -7030,10 +7030,10 @@
         <v>45</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="F253" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G253" t="n">
         <v>11013</v>
@@ -7056,10 +7056,10 @@
         <v>50</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G254" t="n">
         <v>11014</v>
@@ -7082,10 +7082,10 @@
         <v>54</v>
       </c>
       <c r="E255" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G255" t="n">
         <v>11015</v>
@@ -7108,10 +7108,10 @@
         <v>18</v>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G256" t="n">
         <v>11019</v>
@@ -7134,10 +7134,10 @@
         <v>22</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G257" t="n">
         <v>11020</v>
@@ -7160,10 +7160,10 @@
         <v>27</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G258" t="n">
         <v>11011</v>
@@ -7186,10 +7186,10 @@
         <v>32</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G259" t="n">
         <v>11012</v>
@@ -7212,10 +7212,10 @@
         <v>36</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G260" t="n">
         <v>11013</v>
@@ -7238,10 +7238,10 @@
         <v>40</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G261" t="n">
         <v>11014</v>
@@ -7264,10 +7264,10 @@
         <v>45</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G262" t="n">
         <v>11015</v>
@@ -7290,10 +7290,10 @@
         <v>50</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G263" t="n">
         <v>11016</v>
@@ -7316,10 +7316,10 @@
         <v>54</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G264" t="n">
         <v>11017</v>
@@ -7342,10 +7342,10 @@
         <v>24</v>
       </c>
       <c r="E265" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G265" t="n">
         <v>11011</v>
@@ -7368,10 +7368,10 @@
         <v>30</v>
       </c>
       <c r="E266" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="F266" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G266" t="n">
         <v>11012</v>
@@ -7394,10 +7394,10 @@
         <v>36</v>
       </c>
       <c r="E267" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="F267" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G267" t="n">
         <v>11013</v>
@@ -7420,10 +7420,10 @@
         <v>42</v>
       </c>
       <c r="E268" t="n">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="F268" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G268" t="n">
         <v>11014</v>
@@ -7446,10 +7446,10 @@
         <v>48</v>
       </c>
       <c r="E269" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="F269" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G269" t="n">
         <v>11015</v>
@@ -7472,10 +7472,10 @@
         <v>54</v>
       </c>
       <c r="E270" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="F270" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G270" t="n">
         <v>11016</v>
@@ -7498,10 +7498,10 @@
         <v>60</v>
       </c>
       <c r="E271" t="n">
-        <v>0.75</v>
+        <v>7</v>
       </c>
       <c r="F271" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G271" t="n">
         <v>11017</v>
@@ -7524,10 +7524,10 @@
         <v>66</v>
       </c>
       <c r="E272" t="n">
-        <v>0.75</v>
+        <v>8</v>
       </c>
       <c r="F272" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G272" t="n">
         <v>11018</v>
@@ -7550,10 +7550,10 @@
         <v>72</v>
       </c>
       <c r="E273" t="n">
-        <v>0.75</v>
+        <v>9</v>
       </c>
       <c r="F273" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="G273" t="n">
         <v>11019</v>
@@ -7576,10 +7576,10 @@
         <v>66</v>
       </c>
       <c r="E274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G274" t="n">
         <v>11011</v>
@@ -7602,10 +7602,10 @@
         <v>82</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G275" t="n">
         <v>11012</v>
@@ -7628,10 +7628,10 @@
         <v>99</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G276" t="n">
         <v>11013</v>
@@ -7654,10 +7654,10 @@
         <v>116</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G277" t="n">
         <v>11014</v>
@@ -7680,10 +7680,10 @@
         <v>132</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="G278" t="n">
         <v>11015</v>
@@ -7706,10 +7706,10 @@
         <v>148</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G279" t="n">
         <v>11016</v>
@@ -7732,10 +7732,10 @@
         <v>165</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G280" t="n">
         <v>11017</v>
@@ -7758,10 +7758,10 @@
         <v>182</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G281" t="n">
         <v>11018</v>
@@ -7784,10 +7784,10 @@
         <v>198</v>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G282" t="n">
         <v>11019</v>
@@ -7810,10 +7810,10 @@
         <v>19</v>
       </c>
       <c r="E283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G283" t="n">
         <v>11013</v>
@@ -7836,10 +7836,10 @@
         <v>24</v>
       </c>
       <c r="E284" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F284" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G284" t="n">
         <v>11014</v>
@@ -7862,10 +7862,10 @@
         <v>28</v>
       </c>
       <c r="E285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F285" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G285" t="n">
         <v>11015</v>
@@ -7888,10 +7888,10 @@
         <v>33</v>
       </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F286" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G286" t="n">
         <v>11016</v>
@@ -7914,10 +7914,10 @@
         <v>38</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F287" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G287" t="n">
         <v>11017</v>
@@ -7940,10 +7940,10 @@
         <v>43</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F288" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="G288" t="n">
         <v>11018</v>
@@ -7966,10 +7966,10 @@
         <v>48</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F289" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="G289" t="n">
         <v>11019</v>
@@ -7992,10 +7992,10 @@
         <v>52</v>
       </c>
       <c r="E290" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F290" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="G290" t="n">
         <v>11020</v>
@@ -8018,10 +8018,10 @@
         <v>57</v>
       </c>
       <c r="E291" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F291" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G291" t="n">
         <v>11011</v>
@@ -8044,10 +8044,10 @@
         <v>28</v>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G292" t="n">
         <v>11015</v>
@@ -8070,10 +8070,10 @@
         <v>35</v>
       </c>
       <c r="E293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G293" t="n">
         <v>11016</v>
@@ -8096,10 +8096,10 @@
         <v>42</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F294" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G294" t="n">
         <v>11017</v>
@@ -8122,10 +8122,10 @@
         <v>49</v>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G295" t="n">
         <v>11018</v>
@@ -8148,10 +8148,10 @@
         <v>56</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G296" t="n">
         <v>11019</v>
@@ -8174,10 +8174,10 @@
         <v>63</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G297" t="n">
         <v>11020</v>
@@ -8200,10 +8200,10 @@
         <v>70</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G298" t="n">
         <v>11011</v>
@@ -8226,10 +8226,10 @@
         <v>77</v>
       </c>
       <c r="E299" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G299" t="n">
         <v>11012</v>
@@ -8252,10 +8252,10 @@
         <v>84</v>
       </c>
       <c r="E300" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G300" t="n">
         <v>11013</v>
@@ -8278,10 +8278,10 @@
         <v>22</v>
       </c>
       <c r="E301" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G301" t="n">
         <v>11017</v>
@@ -8304,10 +8304,10 @@
         <v>28</v>
       </c>
       <c r="E302" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G302" t="n">
         <v>11018</v>
@@ -8330,10 +8330,10 @@
         <v>33</v>
       </c>
       <c r="E303" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G303" t="n">
         <v>11019</v>
@@ -8356,10 +8356,10 @@
         <v>38</v>
       </c>
       <c r="E304" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G304" t="n">
         <v>11020</v>
@@ -8382,10 +8382,10 @@
         <v>44</v>
       </c>
       <c r="E305" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="F305" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G305" t="n">
         <v>11011</v>
@@ -8408,10 +8408,10 @@
         <v>50</v>
       </c>
       <c r="E306" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G306" t="n">
         <v>11012</v>
@@ -8434,10 +8434,10 @@
         <v>55</v>
       </c>
       <c r="E307" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G307" t="n">
         <v>11013</v>
@@ -8460,10 +8460,10 @@
         <v>60</v>
       </c>
       <c r="E308" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G308" t="n">
         <v>11014</v>
@@ -8486,10 +8486,10 @@
         <v>66</v>
       </c>
       <c r="E309" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G309" t="n">
         <v>11015</v>
@@ -8512,10 +8512,10 @@
         <v>22</v>
       </c>
       <c r="E310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G310" t="n">
         <v>11019</v>
@@ -8538,10 +8538,10 @@
         <v>28</v>
       </c>
       <c r="E311" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G311" t="n">
         <v>11020</v>
@@ -8564,10 +8564,10 @@
         <v>33</v>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G312" t="n">
         <v>11011</v>
@@ -8590,10 +8590,10 @@
         <v>38</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G313" t="n">
         <v>11012</v>
@@ -8616,10 +8616,10 @@
         <v>44</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G314" t="n">
         <v>11013</v>
@@ -8642,10 +8642,10 @@
         <v>50</v>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G315" t="n">
         <v>11014</v>
@@ -8668,10 +8668,10 @@
         <v>55</v>
       </c>
       <c r="E316" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G316" t="n">
         <v>11015</v>
@@ -8694,10 +8694,10 @@
         <v>60</v>
       </c>
       <c r="E317" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F317" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G317" t="n">
         <v>11016</v>
@@ -8720,10 +8720,10 @@
         <v>66</v>
       </c>
       <c r="E318" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G318" t="n">
         <v>11017</v>
@@ -8746,10 +8746,10 @@
         <v>30</v>
       </c>
       <c r="E319" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F319" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G319" t="n">
         <v>11011</v>
@@ -8772,10 +8772,10 @@
         <v>38</v>
       </c>
       <c r="E320" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F320" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G320" t="n">
         <v>11012</v>
@@ -8798,10 +8798,10 @@
         <v>45</v>
       </c>
       <c r="E321" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="F321" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G321" t="n">
         <v>11013</v>
@@ -8824,10 +8824,10 @@
         <v>52</v>
       </c>
       <c r="E322" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="F322" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G322" t="n">
         <v>11014</v>
@@ -8850,10 +8850,10 @@
         <v>60</v>
       </c>
       <c r="E323" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="F323" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G323" t="n">
         <v>11015</v>
@@ -8876,10 +8876,10 @@
         <v>68</v>
       </c>
       <c r="E324" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="F324" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="G324" t="n">
         <v>11016</v>
@@ -8902,10 +8902,10 @@
         <v>75</v>
       </c>
       <c r="E325" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="F325" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="G325" t="n">
         <v>11017</v>
@@ -8928,10 +8928,10 @@
         <v>82</v>
       </c>
       <c r="E326" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="F326" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="G326" t="n">
         <v>11018</v>
@@ -8954,10 +8954,10 @@
         <v>90</v>
       </c>
       <c r="E327" t="n">
-        <v>0.9</v>
+        <v>9</v>
       </c>
       <c r="F327" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="G327" t="n">
         <v>11019</v>
@@ -8980,10 +8980,10 @@
         <v>90</v>
       </c>
       <c r="E328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F328" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G328" t="n">
         <v>11011</v>
@@ -9006,10 +9006,10 @@
         <v>112</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G329" t="n">
         <v>11012</v>
@@ -9032,10 +9032,10 @@
         <v>135</v>
       </c>
       <c r="E330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F330" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="G330" t="n">
         <v>11013</v>
@@ -9058,10 +9058,10 @@
         <v>158</v>
       </c>
       <c r="E331" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F331" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G331" t="n">
         <v>11014</v>
@@ -9084,10 +9084,10 @@
         <v>180</v>
       </c>
       <c r="E332" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G332" t="n">
         <v>11015</v>
@@ -9110,10 +9110,10 @@
         <v>202</v>
       </c>
       <c r="E333" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F333" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="G333" t="n">
         <v>11016</v>
@@ -9136,10 +9136,10 @@
         <v>225</v>
       </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="G334" t="n">
         <v>11017</v>
@@ -9162,10 +9162,10 @@
         <v>248</v>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F335" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="G335" t="n">
         <v>11018</v>
@@ -9188,10 +9188,10 @@
         <v>270</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G336" t="n">
         <v>11019</v>
@@ -9214,10 +9214,10 @@
         <v>26</v>
       </c>
       <c r="E337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F337" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G337" t="n">
         <v>11013</v>
@@ -9240,10 +9240,10 @@
         <v>32</v>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F338" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G338" t="n">
         <v>11014</v>
@@ -9266,10 +9266,10 @@
         <v>39</v>
       </c>
       <c r="E339" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F339" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G339" t="n">
         <v>11015</v>
@@ -9292,10 +9292,10 @@
         <v>46</v>
       </c>
       <c r="E340" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F340" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G340" t="n">
         <v>11016</v>
@@ -9318,10 +9318,10 @@
         <v>52</v>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F341" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="G341" t="n">
         <v>11017</v>
@@ -9344,10 +9344,10 @@
         <v>58</v>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F342" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="G342" t="n">
         <v>11018</v>
@@ -9370,10 +9370,10 @@
         <v>65</v>
       </c>
       <c r="E343" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F343" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="G343" t="n">
         <v>11019</v>
@@ -9396,10 +9396,10 @@
         <v>72</v>
       </c>
       <c r="E344" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F344" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="G344" t="n">
         <v>11020</v>
@@ -9422,10 +9422,10 @@
         <v>78</v>
       </c>
       <c r="E345" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F345" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="G345" t="n">
         <v>11011</v>
@@ -9448,10 +9448,10 @@
         <v>38</v>
       </c>
       <c r="E346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G346" t="n">
         <v>11015</v>
@@ -9474,10 +9474,10 @@
         <v>48</v>
       </c>
       <c r="E347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F347" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G347" t="n">
         <v>11016</v>
@@ -9500,10 +9500,10 @@
         <v>57</v>
       </c>
       <c r="E348" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G348" t="n">
         <v>11017</v>
@@ -9526,10 +9526,10 @@
         <v>66</v>
       </c>
       <c r="E349" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F349" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G349" t="n">
         <v>11018</v>
@@ -9552,10 +9552,10 @@
         <v>76</v>
       </c>
       <c r="E350" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G350" t="n">
         <v>11019</v>
@@ -9578,10 +9578,10 @@
         <v>86</v>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G351" t="n">
         <v>11020</v>
@@ -9604,10 +9604,10 @@
         <v>95</v>
       </c>
       <c r="E352" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G352" t="n">
         <v>11011</v>
@@ -9630,10 +9630,10 @@
         <v>104</v>
       </c>
       <c r="E353" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G353" t="n">
         <v>11012</v>
@@ -9656,10 +9656,10 @@
         <v>114</v>
       </c>
       <c r="E354" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G354" t="n">
         <v>11013</v>
@@ -9682,10 +9682,10 @@
         <v>30</v>
       </c>
       <c r="E355" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F355" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G355" t="n">
         <v>11017</v>
@@ -9708,10 +9708,10 @@
         <v>38</v>
       </c>
       <c r="E356" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G356" t="n">
         <v>11018</v>
@@ -9734,10 +9734,10 @@
         <v>45</v>
       </c>
       <c r="E357" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F357" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G357" t="n">
         <v>11019</v>
@@ -9760,10 +9760,10 @@
         <v>52</v>
       </c>
       <c r="E358" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G358" t="n">
         <v>11020</v>
@@ -9786,10 +9786,10 @@
         <v>60</v>
       </c>
       <c r="E359" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G359" t="n">
         <v>11011</v>
@@ -9812,10 +9812,10 @@
         <v>68</v>
       </c>
       <c r="E360" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G360" t="n">
         <v>11012</v>
@@ -9838,10 +9838,10 @@
         <v>75</v>
       </c>
       <c r="E361" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="F361" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G361" t="n">
         <v>11013</v>
@@ -9864,10 +9864,10 @@
         <v>82</v>
       </c>
       <c r="E362" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="F362" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G362" t="n">
         <v>11014</v>
@@ -9890,10 +9890,10 @@
         <v>90</v>
       </c>
       <c r="E363" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G363" t="n">
         <v>11015</v>
@@ -9916,10 +9916,10 @@
         <v>30</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G364" t="n">
         <v>11019</v>
@@ -9942,10 +9942,10 @@
         <v>38</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G365" t="n">
         <v>11020</v>
@@ -9968,10 +9968,10 @@
         <v>45</v>
       </c>
       <c r="E366" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G366" t="n">
         <v>11011</v>
@@ -9994,10 +9994,10 @@
         <v>52</v>
       </c>
       <c r="E367" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G367" t="n">
         <v>11012</v>
@@ -10020,10 +10020,10 @@
         <v>60</v>
       </c>
       <c r="E368" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F368" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G368" t="n">
         <v>11013</v>
@@ -10046,10 +10046,10 @@
         <v>68</v>
       </c>
       <c r="E369" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F369" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G369" t="n">
         <v>11014</v>
@@ -10072,10 +10072,10 @@
         <v>75</v>
       </c>
       <c r="E370" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G370" t="n">
         <v>11015</v>
@@ -10098,10 +10098,10 @@
         <v>82</v>
       </c>
       <c r="E371" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F371" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G371" t="n">
         <v>11016</v>
@@ -10124,10 +10124,10 @@
         <v>90</v>
       </c>
       <c r="E372" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G372" t="n">
         <v>11017</v>
@@ -10150,10 +10150,10 @@
         <v>41</v>
       </c>
       <c r="E373" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="F373" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G373" t="n">
         <v>11011</v>
@@ -10176,10 +10176,10 @@
         <v>51</v>
       </c>
       <c r="E374" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="F374" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G374" t="n">
         <v>11012</v>
@@ -10202,10 +10202,10 @@
         <v>62</v>
       </c>
       <c r="E375" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="F375" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G375" t="n">
         <v>11013</v>
@@ -10228,10 +10228,10 @@
         <v>72</v>
       </c>
       <c r="E376" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="F376" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="G376" t="n">
         <v>11014</v>
@@ -10254,10 +10254,10 @@
         <v>82</v>
       </c>
       <c r="E377" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="F377" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="G377" t="n">
         <v>11015</v>
@@ -10280,10 +10280,10 @@
         <v>92</v>
       </c>
       <c r="E378" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="F378" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="G378" t="n">
         <v>11016</v>
@@ -10306,10 +10306,10 @@
         <v>102</v>
       </c>
       <c r="E379" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="F379" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="G379" t="n">
         <v>11017</v>
@@ -10332,10 +10332,10 @@
         <v>113</v>
       </c>
       <c r="E380" t="n">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="F380" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="G380" t="n">
         <v>11018</v>
@@ -10358,10 +10358,10 @@
         <v>123</v>
       </c>
       <c r="E381" t="n">
-        <v>1.05</v>
+        <v>9</v>
       </c>
       <c r="F381" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="G381" t="n">
         <v>11019</v>
@@ -10384,10 +10384,10 @@
         <v>114</v>
       </c>
       <c r="E382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G382" t="n">
         <v>11021</v>
@@ -10410,10 +10410,10 @@
         <v>142</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G383" t="n">
         <v>11022</v>
@@ -10436,10 +10436,10 @@
         <v>171</v>
       </c>
       <c r="E384" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F384" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G384" t="n">
         <v>11023</v>
@@ -10462,10 +10462,10 @@
         <v>200</v>
       </c>
       <c r="E385" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G385" t="n">
         <v>11024</v>
@@ -10488,10 +10488,10 @@
         <v>228</v>
       </c>
       <c r="E386" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F386" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="G386" t="n">
         <v>11025</v>
@@ -10514,10 +10514,10 @@
         <v>256</v>
       </c>
       <c r="E387" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F387" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="G387" t="n">
         <v>11026</v>
@@ -10540,10 +10540,10 @@
         <v>285</v>
       </c>
       <c r="E388" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F388" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="G388" t="n">
         <v>11027</v>
@@ -10566,10 +10566,10 @@
         <v>314</v>
       </c>
       <c r="E389" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F389" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="G389" t="n">
         <v>11028</v>
@@ -10592,10 +10592,10 @@
         <v>342</v>
       </c>
       <c r="E390" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F390" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="G390" t="n">
         <v>11029</v>
@@ -10618,10 +10618,10 @@
         <v>32</v>
       </c>
       <c r="E391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F391" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G391" t="n">
         <v>11023</v>
@@ -10644,10 +10644,10 @@
         <v>40</v>
       </c>
       <c r="E392" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F392" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G392" t="n">
         <v>11024</v>
@@ -10670,10 +10670,10 @@
         <v>48</v>
       </c>
       <c r="E393" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F393" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="G393" t="n">
         <v>11025</v>
@@ -10696,10 +10696,10 @@
         <v>56</v>
       </c>
       <c r="E394" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F394" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G394" t="n">
         <v>11026</v>
@@ -10722,10 +10722,10 @@
         <v>64</v>
       </c>
       <c r="E395" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F395" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="G395" t="n">
         <v>11027</v>
@@ -10748,10 +10748,10 @@
         <v>72</v>
       </c>
       <c r="E396" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F396" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G396" t="n">
         <v>11028</v>
@@ -10774,10 +10774,10 @@
         <v>80</v>
       </c>
       <c r="E397" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F397" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G397" t="n">
         <v>11029</v>
@@ -10800,10 +10800,10 @@
         <v>88</v>
       </c>
       <c r="E398" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F398" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="G398" t="n">
         <v>11030</v>
@@ -10826,10 +10826,10 @@
         <v>96</v>
       </c>
       <c r="E399" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F399" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="G399" t="n">
         <v>11021</v>
@@ -10852,10 +10852,10 @@
         <v>48</v>
       </c>
       <c r="E400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F400" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G400" t="n">
         <v>11025</v>
@@ -10878,10 +10878,10 @@
         <v>60</v>
       </c>
       <c r="E401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G401" t="n">
         <v>11026</v>
@@ -10904,10 +10904,10 @@
         <v>72</v>
       </c>
       <c r="E402" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F402" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G402" t="n">
         <v>11027</v>
@@ -10930,10 +10930,10 @@
         <v>84</v>
       </c>
       <c r="E403" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F403" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G403" t="n">
         <v>11028</v>
@@ -10956,10 +10956,10 @@
         <v>96</v>
       </c>
       <c r="E404" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F404" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G404" t="n">
         <v>11029</v>
@@ -10982,10 +10982,10 @@
         <v>108</v>
       </c>
       <c r="E405" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F405" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G405" t="n">
         <v>11030</v>
@@ -11008,10 +11008,10 @@
         <v>120</v>
       </c>
       <c r="E406" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F406" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="G406" t="n">
         <v>11021</v>
@@ -11034,10 +11034,10 @@
         <v>132</v>
       </c>
       <c r="E407" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="G407" t="n">
         <v>11022</v>
@@ -11060,10 +11060,10 @@
         <v>144</v>
       </c>
       <c r="E408" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F408" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G408" t="n">
         <v>11023</v>
@@ -11086,10 +11086,10 @@
         <v>39</v>
       </c>
       <c r="E409" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F409" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G409" t="n">
         <v>11027</v>
@@ -11112,10 +11112,10 @@
         <v>49</v>
       </c>
       <c r="E410" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="F410" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G410" t="n">
         <v>11028</v>
@@ -11138,10 +11138,10 @@
         <v>58</v>
       </c>
       <c r="E411" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F411" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G411" t="n">
         <v>11029</v>
@@ -11164,10 +11164,10 @@
         <v>68</v>
       </c>
       <c r="E412" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="F412" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G412" t="n">
         <v>11030</v>
@@ -11190,10 +11190,10 @@
         <v>78</v>
       </c>
       <c r="E413" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G413" t="n">
         <v>11021</v>
@@ -11216,10 +11216,10 @@
         <v>88</v>
       </c>
       <c r="E414" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="F414" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G414" t="n">
         <v>11022</v>
@@ -11242,10 +11242,10 @@
         <v>98</v>
       </c>
       <c r="E415" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="F415" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G415" t="n">
         <v>11023</v>
@@ -11268,10 +11268,10 @@
         <v>107</v>
       </c>
       <c r="E416" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="F416" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G416" t="n">
         <v>11024</v>
@@ -11294,10 +11294,10 @@
         <v>117</v>
       </c>
       <c r="E417" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="F417" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G417" t="n">
         <v>11025</v>
@@ -11320,10 +11320,10 @@
         <v>39</v>
       </c>
       <c r="E418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G418" t="n">
         <v>11029</v>
@@ -11346,10 +11346,10 @@
         <v>49</v>
       </c>
       <c r="E419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F419" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G419" t="n">
         <v>11030</v>
@@ -11372,10 +11372,10 @@
         <v>58</v>
       </c>
       <c r="E420" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F420" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G420" t="n">
         <v>11021</v>
@@ -11398,10 +11398,10 @@
         <v>68</v>
       </c>
       <c r="E421" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F421" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G421" t="n">
         <v>11022</v>
@@ -11424,10 +11424,10 @@
         <v>78</v>
       </c>
       <c r="E422" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F422" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G422" t="n">
         <v>11023</v>
@@ -11450,10 +11450,10 @@
         <v>88</v>
       </c>
       <c r="E423" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G423" t="n">
         <v>11024</v>
@@ -11476,10 +11476,10 @@
         <v>98</v>
       </c>
       <c r="E424" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F424" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G424" t="n">
         <v>11025</v>
@@ -11502,10 +11502,10 @@
         <v>107</v>
       </c>
       <c r="E425" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F425" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G425" t="n">
         <v>11026</v>
@@ -11528,10 +11528,10 @@
         <v>117</v>
       </c>
       <c r="E426" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G426" t="n">
         <v>11027</v>
@@ -11554,10 +11554,10 @@
         <v>52</v>
       </c>
       <c r="E427" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F427" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G427" t="n">
         <v>11021</v>
@@ -11580,10 +11580,10 @@
         <v>65</v>
       </c>
       <c r="E428" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="F428" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G428" t="n">
         <v>11022</v>
@@ -11606,10 +11606,10 @@
         <v>78</v>
       </c>
       <c r="E429" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="F429" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="G429" t="n">
         <v>11023</v>
@@ -11632,10 +11632,10 @@
         <v>91</v>
       </c>
       <c r="E430" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="F430" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="G430" t="n">
         <v>11024</v>
@@ -11658,10 +11658,10 @@
         <v>104</v>
       </c>
       <c r="E431" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="F431" t="n">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G431" t="n">
         <v>11025</v>
@@ -11684,10 +11684,10 @@
         <v>117</v>
       </c>
       <c r="E432" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="F432" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="G432" t="n">
         <v>11026</v>
@@ -11710,10 +11710,10 @@
         <v>130</v>
       </c>
       <c r="E433" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="F433" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="G433" t="n">
         <v>11027</v>
@@ -11736,10 +11736,10 @@
         <v>143</v>
       </c>
       <c r="E434" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="F434" t="n">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="G434" t="n">
         <v>11028</v>
@@ -11762,10 +11762,10 @@
         <v>156</v>
       </c>
       <c r="E435" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="F435" t="n">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="G435" t="n">
         <v>11029</v>
@@ -11788,10 +11788,10 @@
         <v>146</v>
       </c>
       <c r="E436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F436" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="G436" t="n">
         <v>11021</v>
@@ -11814,10 +11814,10 @@
         <v>182</v>
       </c>
       <c r="E437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F437" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G437" t="n">
         <v>11022</v>
@@ -11840,10 +11840,10 @@
         <v>219</v>
       </c>
       <c r="E438" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F438" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="G438" t="n">
         <v>11023</v>
@@ -11866,10 +11866,10 @@
         <v>256</v>
       </c>
       <c r="E439" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="G439" t="n">
         <v>11024</v>
@@ -11892,10 +11892,10 @@
         <v>292</v>
       </c>
       <c r="E440" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F440" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="G440" t="n">
         <v>11025</v>
@@ -11918,10 +11918,10 @@
         <v>328</v>
       </c>
       <c r="E441" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F441" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="G441" t="n">
         <v>11026</v>
@@ -11944,10 +11944,10 @@
         <v>365</v>
       </c>
       <c r="E442" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F442" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G442" t="n">
         <v>11027</v>
@@ -11970,10 +11970,10 @@
         <v>402</v>
       </c>
       <c r="E443" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F443" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="G443" t="n">
         <v>11028</v>
@@ -11996,10 +11996,10 @@
         <v>438</v>
       </c>
       <c r="E444" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F444" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G444" t="n">
         <v>11029</v>
@@ -12022,10 +12022,10 @@
         <v>42</v>
       </c>
       <c r="E445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F445" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G445" t="n">
         <v>11023</v>
@@ -12048,10 +12048,10 @@
         <v>52</v>
       </c>
       <c r="E446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F446" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="G446" t="n">
         <v>11024</v>
@@ -12074,10 +12074,10 @@
         <v>63</v>
       </c>
       <c r="E447" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F447" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G447" t="n">
         <v>11025</v>
@@ -12100,10 +12100,10 @@
         <v>74</v>
       </c>
       <c r="E448" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F448" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="G448" t="n">
         <v>11026</v>
@@ -12126,10 +12126,10 @@
         <v>84</v>
       </c>
       <c r="E449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F449" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="G449" t="n">
         <v>11027</v>
@@ -12152,10 +12152,10 @@
         <v>94</v>
       </c>
       <c r="E450" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F450" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="G450" t="n">
         <v>11028</v>
@@ -12178,10 +12178,10 @@
         <v>105</v>
       </c>
       <c r="E451" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F451" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="G451" t="n">
         <v>11029</v>
@@ -12204,10 +12204,10 @@
         <v>116</v>
       </c>
       <c r="E452" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F452" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="G452" t="n">
         <v>11030</v>
@@ -12230,10 +12230,10 @@
         <v>126</v>
       </c>
       <c r="E453" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F453" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="G453" t="n">
         <v>11021</v>
@@ -12256,10 +12256,10 @@
         <v>62</v>
       </c>
       <c r="E454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F454" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G454" t="n">
         <v>11025</v>
@@ -12282,10 +12282,10 @@
         <v>78</v>
       </c>
       <c r="E455" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F455" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G455" t="n">
         <v>11026</v>
@@ -12308,10 +12308,10 @@
         <v>93</v>
       </c>
       <c r="E456" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F456" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G456" t="n">
         <v>11027</v>
@@ -12334,10 +12334,10 @@
         <v>108</v>
       </c>
       <c r="E457" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F457" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G457" t="n">
         <v>11028</v>
@@ -12360,10 +12360,10 @@
         <v>124</v>
       </c>
       <c r="E458" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F458" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G458" t="n">
         <v>11029</v>
@@ -12386,10 +12386,10 @@
         <v>140</v>
       </c>
       <c r="E459" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F459" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G459" t="n">
         <v>11030</v>
@@ -12412,10 +12412,10 @@
         <v>155</v>
       </c>
       <c r="E460" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F460" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G460" t="n">
         <v>11021</v>
@@ -12438,10 +12438,10 @@
         <v>170</v>
       </c>
       <c r="E461" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F461" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G461" t="n">
         <v>11022</v>
@@ -12464,10 +12464,10 @@
         <v>186</v>
       </c>
       <c r="E462" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F462" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G462" t="n">
         <v>11023</v>
@@ -12490,10 +12490,10 @@
         <v>50</v>
       </c>
       <c r="E463" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F463" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G463" t="n">
         <v>11027</v>
@@ -12516,10 +12516,10 @@
         <v>62</v>
       </c>
       <c r="E464" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F464" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G464" t="n">
         <v>11028</v>
@@ -12542,10 +12542,10 @@
         <v>75</v>
       </c>
       <c r="E465" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="F465" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G465" t="n">
         <v>11029</v>
@@ -12568,10 +12568,10 @@
         <v>88</v>
       </c>
       <c r="E466" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="F466" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G466" t="n">
         <v>11030</v>
@@ -12594,10 +12594,10 @@
         <v>100</v>
       </c>
       <c r="E467" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="F467" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G467" t="n">
         <v>11021</v>
@@ -12620,10 +12620,10 @@
         <v>112</v>
       </c>
       <c r="E468" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="F468" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G468" t="n">
         <v>11022</v>
@@ -12646,10 +12646,10 @@
         <v>125</v>
       </c>
       <c r="E469" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="F469" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G469" t="n">
         <v>11023</v>
@@ -12672,10 +12672,10 @@
         <v>138</v>
       </c>
       <c r="E470" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="F470" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G470" t="n">
         <v>11024</v>
@@ -12698,10 +12698,10 @@
         <v>150</v>
       </c>
       <c r="E471" t="n">
-        <v>0.9</v>
+        <v>9</v>
       </c>
       <c r="F471" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G471" t="n">
         <v>11025</v>
@@ -12724,10 +12724,10 @@
         <v>50</v>
       </c>
       <c r="E472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F472" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G472" t="n">
         <v>11029</v>
@@ -12750,10 +12750,10 @@
         <v>62</v>
       </c>
       <c r="E473" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F473" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G473" t="n">
         <v>11030</v>
@@ -12776,10 +12776,10 @@
         <v>75</v>
       </c>
       <c r="E474" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F474" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G474" t="n">
         <v>11021</v>
@@ -12802,10 +12802,10 @@
         <v>88</v>
       </c>
       <c r="E475" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F475" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G475" t="n">
         <v>11022</v>
@@ -12828,10 +12828,10 @@
         <v>100</v>
       </c>
       <c r="E476" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F476" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G476" t="n">
         <v>11023</v>
@@ -12854,10 +12854,10 @@
         <v>112</v>
       </c>
       <c r="E477" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F477" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G477" t="n">
         <v>11024</v>
@@ -12880,10 +12880,10 @@
         <v>125</v>
       </c>
       <c r="E478" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F478" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G478" t="n">
         <v>11025</v>
@@ -12906,10 +12906,10 @@
         <v>138</v>
       </c>
       <c r="E479" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F479" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G479" t="n">
         <v>11026</v>
@@ -12932,10 +12932,10 @@
         <v>150</v>
       </c>
       <c r="E480" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F480" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G480" t="n">
         <v>11027</v>
@@ -12958,10 +12958,10 @@
         <v>66</v>
       </c>
       <c r="E481" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="F481" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="G481" t="n">
         <v>11021</v>
@@ -12984,10 +12984,10 @@
         <v>82</v>
       </c>
       <c r="E482" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="F482" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="G482" t="n">
         <v>11022</v>
@@ -13010,10 +13010,10 @@
         <v>99</v>
       </c>
       <c r="E483" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="F483" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="G483" t="n">
         <v>11023</v>
@@ -13036,10 +13036,10 @@
         <v>116</v>
       </c>
       <c r="E484" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="F484" t="n">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="G484" t="n">
         <v>11024</v>
@@ -13062,10 +13062,10 @@
         <v>132</v>
       </c>
       <c r="E485" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="F485" t="n">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="G485" t="n">
         <v>11025</v>
@@ -13088,10 +13088,10 @@
         <v>148</v>
       </c>
       <c r="E486" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="F486" t="n">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="G486" t="n">
         <v>11026</v>
@@ -13114,10 +13114,10 @@
         <v>165</v>
       </c>
       <c r="E487" t="n">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="F487" t="n">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="G487" t="n">
         <v>11027</v>
@@ -13140,10 +13140,10 @@
         <v>182</v>
       </c>
       <c r="E488" t="n">
-        <v>1.35</v>
+        <v>8</v>
       </c>
       <c r="F488" t="n">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="G488" t="n">
         <v>11028</v>
@@ -13166,10 +13166,10 @@
         <v>198</v>
       </c>
       <c r="E489" t="n">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="F489" t="n">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="G489" t="n">
         <v>11029</v>
@@ -13192,10 +13192,10 @@
         <v>182</v>
       </c>
       <c r="E490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F490" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G490" t="n">
         <v>11021</v>
@@ -13218,10 +13218,10 @@
         <v>228</v>
       </c>
       <c r="E491" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F491" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="G491" t="n">
         <v>11022</v>
@@ -13244,10 +13244,10 @@
         <v>273</v>
       </c>
       <c r="E492" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F492" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="G492" t="n">
         <v>11023</v>
@@ -13270,10 +13270,10 @@
         <v>318</v>
       </c>
       <c r="E493" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F493" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="G493" t="n">
         <v>11024</v>
@@ -13296,10 +13296,10 @@
         <v>364</v>
       </c>
       <c r="E494" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F494" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G494" t="n">
         <v>11025</v>
@@ -13322,10 +13322,10 @@
         <v>410</v>
       </c>
       <c r="E495" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F495" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G495" t="n">
         <v>11026</v>
@@ -13348,10 +13348,10 @@
         <v>455</v>
       </c>
       <c r="E496" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F496" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="G496" t="n">
         <v>11027</v>
@@ -13374,10 +13374,10 @@
         <v>500</v>
       </c>
       <c r="E497" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F497" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="G497" t="n">
         <v>11028</v>
@@ -13400,10 +13400,10 @@
         <v>546</v>
       </c>
       <c r="E498" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F498" t="n">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="G498" t="n">
         <v>11029</v>
@@ -13426,10 +13426,10 @@
         <v>52</v>
       </c>
       <c r="E499" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F499" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="G499" t="n">
         <v>11023</v>
@@ -13452,10 +13452,10 @@
         <v>65</v>
       </c>
       <c r="E500" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F500" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G500" t="n">
         <v>11024</v>
@@ -13478,10 +13478,10 @@
         <v>78</v>
       </c>
       <c r="E501" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F501" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="G501" t="n">
         <v>11025</v>
@@ -13504,10 +13504,10 @@
         <v>91</v>
       </c>
       <c r="E502" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F502" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G502" t="n">
         <v>11026</v>
@@ -13530,10 +13530,10 @@
         <v>104</v>
       </c>
       <c r="E503" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F503" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G503" t="n">
         <v>11027</v>
@@ -13556,10 +13556,10 @@
         <v>117</v>
       </c>
       <c r="E504" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F504" t="n">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="G504" t="n">
         <v>11028</v>
@@ -13582,10 +13582,10 @@
         <v>130</v>
       </c>
       <c r="E505" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F505" t="n">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="G505" t="n">
         <v>11029</v>
@@ -13608,10 +13608,10 @@
         <v>143</v>
       </c>
       <c r="E506" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F506" t="n">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="G506" t="n">
         <v>11030</v>
@@ -13634,10 +13634,10 @@
         <v>156</v>
       </c>
       <c r="E507" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F507" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G507" t="n">
         <v>11021</v>
@@ -13660,10 +13660,10 @@
         <v>78</v>
       </c>
       <c r="E508" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F508" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G508" t="n">
         <v>11025</v>
@@ -13686,10 +13686,10 @@
         <v>98</v>
       </c>
       <c r="E509" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F509" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G509" t="n">
         <v>11026</v>
@@ -13712,10 +13712,10 @@
         <v>117</v>
       </c>
       <c r="E510" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F510" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G510" t="n">
         <v>11027</v>
@@ -13738,10 +13738,10 @@
         <v>136</v>
       </c>
       <c r="E511" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F511" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="G511" t="n">
         <v>11028</v>
@@ -13764,10 +13764,10 @@
         <v>156</v>
       </c>
       <c r="E512" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F512" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G512" t="n">
         <v>11029</v>
@@ -13790,10 +13790,10 @@
         <v>176</v>
       </c>
       <c r="E513" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F513" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="G513" t="n">
         <v>11030</v>
@@ -13816,10 +13816,10 @@
         <v>195</v>
       </c>
       <c r="E514" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F514" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="G514" t="n">
         <v>11021</v>
@@ -13842,10 +13842,10 @@
         <v>214</v>
       </c>
       <c r="E515" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F515" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="G515" t="n">
         <v>11022</v>
@@ -13868,10 +13868,10 @@
         <v>234</v>
       </c>
       <c r="E516" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F516" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="G516" t="n">
         <v>11023</v>
@@ -13897,7 +13897,7 @@
         <v>1</v>
       </c>
       <c r="F517" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G517" t="n">
         <v>11027</v>
@@ -13920,10 +13920,10 @@
         <v>78</v>
       </c>
       <c r="E518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F518" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G518" t="n">
         <v>11028</v>
@@ -13946,10 +13946,10 @@
         <v>93</v>
       </c>
       <c r="E519" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F519" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G519" t="n">
         <v>11029</v>
@@ -13972,10 +13972,10 @@
         <v>108</v>
       </c>
       <c r="E520" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F520" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G520" t="n">
         <v>11030</v>
@@ -13998,10 +13998,10 @@
         <v>124</v>
       </c>
       <c r="E521" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F521" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G521" t="n">
         <v>11021</v>
@@ -14024,10 +14024,10 @@
         <v>140</v>
       </c>
       <c r="E522" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F522" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G522" t="n">
         <v>11022</v>
@@ -14050,10 +14050,10 @@
         <v>155</v>
       </c>
       <c r="E523" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F523" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G523" t="n">
         <v>11023</v>
@@ -14076,10 +14076,10 @@
         <v>170</v>
       </c>
       <c r="E524" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F524" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G524" t="n">
         <v>11024</v>
@@ -14102,10 +14102,10 @@
         <v>186</v>
       </c>
       <c r="E525" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F525" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G525" t="n">
         <v>11025</v>
@@ -14128,10 +14128,10 @@
         <v>62</v>
       </c>
       <c r="E526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F526" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G526" t="n">
         <v>11029</v>
@@ -14154,10 +14154,10 @@
         <v>78</v>
       </c>
       <c r="E527" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F527" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G527" t="n">
         <v>11030</v>
@@ -14180,10 +14180,10 @@
         <v>93</v>
       </c>
       <c r="E528" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F528" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G528" t="n">
         <v>11021</v>
@@ -14206,10 +14206,10 @@
         <v>108</v>
       </c>
       <c r="E529" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F529" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G529" t="n">
         <v>11022</v>
@@ -14232,10 +14232,10 @@
         <v>124</v>
       </c>
       <c r="E530" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F530" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G530" t="n">
         <v>11023</v>
@@ -14258,10 +14258,10 @@
         <v>140</v>
       </c>
       <c r="E531" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F531" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G531" t="n">
         <v>11024</v>
@@ -14284,10 +14284,10 @@
         <v>155</v>
       </c>
       <c r="E532" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F532" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G532" t="n">
         <v>11025</v>
@@ -14310,10 +14310,10 @@
         <v>170</v>
       </c>
       <c r="E533" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F533" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G533" t="n">
         <v>11026</v>
@@ -14336,10 +14336,10 @@
         <v>186</v>
       </c>
       <c r="E534" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F534" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G534" t="n">
         <v>11027</v>
@@ -14362,10 +14362,10 @@
         <v>84</v>
       </c>
       <c r="E535" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F535" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="G535" t="n">
         <v>11021</v>
@@ -14388,10 +14388,10 @@
         <v>105</v>
       </c>
       <c r="E536" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F536" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="G536" t="n">
         <v>11022</v>
@@ -14414,10 +14414,10 @@
         <v>126</v>
       </c>
       <c r="E537" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F537" t="n">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G537" t="n">
         <v>11023</v>
@@ -14440,10 +14440,10 @@
         <v>147</v>
       </c>
       <c r="E538" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F538" t="n">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="G538" t="n">
         <v>11024</v>
@@ -14466,10 +14466,10 @@
         <v>168</v>
       </c>
       <c r="E539" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="F539" t="n">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="G539" t="n">
         <v>11025</v>
@@ -14492,10 +14492,10 @@
         <v>189</v>
       </c>
       <c r="E540" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="F540" t="n">
-        <v>42</v>
+        <v>170</v>
       </c>
       <c r="G540" t="n">
         <v>11026</v>
@@ -14518,10 +14518,10 @@
         <v>210</v>
       </c>
       <c r="E541" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="F541" t="n">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="G541" t="n">
         <v>11027</v>
@@ -14544,10 +14544,10 @@
         <v>231</v>
       </c>
       <c r="E542" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="F542" t="n">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="G542" t="n">
         <v>11028</v>
@@ -14570,10 +14570,10 @@
         <v>252</v>
       </c>
       <c r="E543" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="F543" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="G543" t="n">
         <v>11029</v>

--- a/Assets/@Resources/Data/Excel/EquipEnhanceData.xlsx
+++ b/Assets/@Resources/Data/Excel/EquipEnhanceData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:H561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14582,6 +14582,474 @@
         <v>37</v>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>541</v>
+      </c>
+      <c r="B544" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C544" t="n">
+        <v>1</v>
+      </c>
+      <c r="D544" t="n">
+        <v>9</v>
+      </c>
+      <c r="E544" t="n">
+        <v>0</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H544" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>542</v>
+      </c>
+      <c r="B545" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C545" t="n">
+        <v>2</v>
+      </c>
+      <c r="D545" t="n">
+        <v>9</v>
+      </c>
+      <c r="E545" t="n">
+        <v>0</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H545" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>543</v>
+      </c>
+      <c r="B546" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C546" t="n">
+        <v>3</v>
+      </c>
+      <c r="D546" t="n">
+        <v>9</v>
+      </c>
+      <c r="E546" t="n">
+        <v>0</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0</v>
+      </c>
+      <c r="G546" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H546" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>544</v>
+      </c>
+      <c r="B547" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C547" t="n">
+        <v>4</v>
+      </c>
+      <c r="D547" t="n">
+        <v>9</v>
+      </c>
+      <c r="E547" t="n">
+        <v>0</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H547" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>545</v>
+      </c>
+      <c r="B548" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C548" t="n">
+        <v>5</v>
+      </c>
+      <c r="D548" t="n">
+        <v>9</v>
+      </c>
+      <c r="E548" t="n">
+        <v>0</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H548" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>546</v>
+      </c>
+      <c r="B549" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C549" t="n">
+        <v>6</v>
+      </c>
+      <c r="D549" t="n">
+        <v>9</v>
+      </c>
+      <c r="E549" t="n">
+        <v>0</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0</v>
+      </c>
+      <c r="G549" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H549" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>547</v>
+      </c>
+      <c r="B550" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C550" t="n">
+        <v>7</v>
+      </c>
+      <c r="D550" t="n">
+        <v>9</v>
+      </c>
+      <c r="E550" t="n">
+        <v>0</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H550" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>548</v>
+      </c>
+      <c r="B551" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C551" t="n">
+        <v>8</v>
+      </c>
+      <c r="D551" t="n">
+        <v>9</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H551" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>549</v>
+      </c>
+      <c r="B552" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C552" t="n">
+        <v>9</v>
+      </c>
+      <c r="D552" t="n">
+        <v>9</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H552" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>550</v>
+      </c>
+      <c r="B553" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C553" t="n">
+        <v>1</v>
+      </c>
+      <c r="D553" t="n">
+        <v>7</v>
+      </c>
+      <c r="E553" t="n">
+        <v>0</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H553" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>551</v>
+      </c>
+      <c r="B554" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C554" t="n">
+        <v>2</v>
+      </c>
+      <c r="D554" t="n">
+        <v>7</v>
+      </c>
+      <c r="E554" t="n">
+        <v>0</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H554" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>552</v>
+      </c>
+      <c r="B555" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C555" t="n">
+        <v>3</v>
+      </c>
+      <c r="D555" t="n">
+        <v>7</v>
+      </c>
+      <c r="E555" t="n">
+        <v>0</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0</v>
+      </c>
+      <c r="G555" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H555" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>553</v>
+      </c>
+      <c r="B556" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C556" t="n">
+        <v>4</v>
+      </c>
+      <c r="D556" t="n">
+        <v>7</v>
+      </c>
+      <c r="E556" t="n">
+        <v>0</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H556" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>554</v>
+      </c>
+      <c r="B557" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C557" t="n">
+        <v>5</v>
+      </c>
+      <c r="D557" t="n">
+        <v>7</v>
+      </c>
+      <c r="E557" t="n">
+        <v>0</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0</v>
+      </c>
+      <c r="G557" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H557" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>555</v>
+      </c>
+      <c r="B558" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C558" t="n">
+        <v>6</v>
+      </c>
+      <c r="D558" t="n">
+        <v>7</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H558" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>556</v>
+      </c>
+      <c r="B559" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C559" t="n">
+        <v>7</v>
+      </c>
+      <c r="D559" t="n">
+        <v>7</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0</v>
+      </c>
+      <c r="G559" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H559" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>557</v>
+      </c>
+      <c r="B560" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C560" t="n">
+        <v>8</v>
+      </c>
+      <c r="D560" t="n">
+        <v>7</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H560" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>558</v>
+      </c>
+      <c r="B561" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C561" t="n">
+        <v>9</v>
+      </c>
+      <c r="D561" t="n">
+        <v>7</v>
+      </c>
+      <c r="E561" t="n">
+        <v>0</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0</v>
+      </c>
+      <c r="G561" t="n">
+        <v>11001</v>
+      </c>
+      <c r="H561" t="n">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
